--- a/fixtures/xlsx/comments/input.xlsx
+++ b/fixtures/xlsx/comments/input.xlsx
@@ -27,16 +27,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>important value</t>
+    <t>Data</t>
   </si>
   <si>
     <t>see comment</t>
   </si>
   <si>
-    <t>Data</t>
+    <t>Notes</t>
   </si>
   <si>
-    <t>Notes</t>
+    <t>important value</t>
   </si>
 </sst>
 </file>
@@ -46,15 +46,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>

--- a/fixtures/xlsx/comments/input.xlsx
+++ b/fixtures/xlsx/comments/input.xlsx
@@ -30,13 +30,13 @@
     <t>Data</t>
   </si>
   <si>
-    <t>see comment</t>
+    <t>important value</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>important value</t>
+    <t>see comment</t>
   </si>
 </sst>
 </file>
@@ -54,10 +54,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
